--- a/SoRoSim Robots/my_robot(2.00to1.25)(3tendon)/10-09-2025/Validation(2.00to1.25)(3tendon).xlsx
+++ b/SoRoSim Robots/my_robot(2.00to1.25)(3tendon)/10-09-2025/Validation(2.00to1.25)(3tendon).xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/SoRoSim Robots/my_robot(2.00to1.25)(3tendon)/10-09-2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1976" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66C8751A-230F-43B3-B2FD-3A1886D14055}"/>
+  <xr:revisionPtr revIDLastSave="1987" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4281DC6E-EFA6-4C7D-A5B5-B12B975F6A1E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation (single)" sheetId="8" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="11" r:id="rId2"/>
-    <sheet name="Distal Validation (single)" sheetId="9" r:id="rId3"/>
-    <sheet name="Distal Vali (single, w noise)" sheetId="12" r:id="rId4"/>
+    <sheet name="Distal Validation (single)" sheetId="9" r:id="rId2"/>
+    <sheet name="Distal Vali (0.2 prop noise)" sheetId="12" r:id="rId3"/>
+    <sheet name="Distal Vali (add noise)" sheetId="14" r:id="rId4"/>
     <sheet name="Conversion" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="13" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="33">
   <si>
     <t>Fx (N)</t>
   </si>
@@ -391,6 +392,12 @@
     <xf numFmtId="164" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -403,12 +410,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -418,19 +419,19 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -787,37 +788,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F22B4A24-01F9-43FA-AE7F-5A1710EEAA53}">
   <dimension ref="A1:Y17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:25" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="12" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="14" t="s">
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
       <c r="T1" s="18" t="s">
         <v>16</v>
       </c>
@@ -827,7 +828,7 @@
       <c r="X1" s="19"/>
       <c r="Y1" s="20"/>
     </row>
-    <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,7 +905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
         <v>0.3</v>
       </c>
@@ -987,7 +988,7 @@
         <v>2.8591807428352489E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>0.4</v>
       </c>
@@ -1070,7 +1071,7 @@
         <v>4.1070231529533097E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <v>0.6</v>
       </c>
@@ -1153,7 +1154,7 @@
         <v>1.8286187751601068E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <v>0.4</v>
       </c>
@@ -1236,7 +1237,7 @@
         <v>2.4117212577145886E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <v>0.8</v>
       </c>
@@ -1319,7 +1320,7 @@
         <v>3.3252255824195665E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <v>0.7</v>
       </c>
@@ -1402,7 +1403,7 @@
         <v>0.12227210880421968</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <v>0.7</v>
       </c>
@@ -1485,7 +1486,7 @@
         <v>0.11008057164375779</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <v>0.7</v>
       </c>
@@ -1568,7 +1569,7 @@
         <v>3.3164222224521811E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <v>0.6</v>
       </c>
@@ -1651,7 +1652,7 @@
         <v>4.6064193052809399E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <v>0.8</v>
       </c>
@@ -1734,7 +1735,7 @@
         <v>5.9957476449353009E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <v>0.4</v>
       </c>
@@ -1817,7 +1818,7 @@
         <v>4.3866582491072462E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
         <v>0.4</v>
       </c>
@@ -1900,7 +1901,7 @@
         <v>1.454992354463075E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
         <v>0.7</v>
       </c>
@@ -1983,7 +1984,7 @@
         <v>1.9276471606230472E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
         <v>0.4</v>
       </c>
@@ -2066,7 +2067,7 @@
         <v>2.2849509346787616E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" s="11">
         <v>0.3</v>
       </c>
@@ -2162,513 +2163,68 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF8CE61A-219E-4DE5-8E04-F5B1F6E7E6E5}">
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>2.6342464843764901E-4</v>
-      </c>
-      <c r="B1">
-        <v>-3.2978262752294499E-2</v>
-      </c>
-      <c r="C1">
-        <v>5.6162860710173802E-4</v>
-      </c>
-      <c r="D1">
-        <v>0.185834720730782</v>
-      </c>
-      <c r="E1">
-        <v>1.13257020711899E-3</v>
-      </c>
-      <c r="F1">
-        <v>0.19288232922553999</v>
-      </c>
-      <c r="G1">
-        <v>1.4</v>
-      </c>
-      <c r="H1">
-        <v>0</v>
-      </c>
-      <c r="I1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>-4.3474312406033299E-4</v>
-      </c>
-      <c r="B2">
-        <v>-6.2425632029771798E-2</v>
-      </c>
-      <c r="C2">
-        <v>2.5845002382993698E-3</v>
-      </c>
-      <c r="D2">
-        <v>0.25303724408149703</v>
-      </c>
-      <c r="E2">
-        <v>1.07369087636471E-2</v>
-      </c>
-      <c r="F2">
-        <v>0.27653545141220098</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>5.3234044462442398E-3</v>
-      </c>
-      <c r="B3">
-        <v>-0.12275674194097499</v>
-      </c>
-      <c r="C3">
-        <v>-8.3989212289452605E-3</v>
-      </c>
-      <c r="D3">
-        <v>0.26806160807609603</v>
-      </c>
-      <c r="E3">
-        <v>-2.4467468261718799E-2</v>
-      </c>
-      <c r="F3">
-        <v>0.52633810043335005</v>
-      </c>
-      <c r="G3">
-        <v>1.4</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>6.7002582363784302E-4</v>
-      </c>
-      <c r="B4">
-        <v>-6.6750191152095795E-2</v>
-      </c>
-      <c r="C4">
-        <v>1.6002767952158999E-3</v>
-      </c>
-      <c r="D4">
-        <v>-3.97013984620571E-2</v>
-      </c>
-      <c r="E4">
-        <v>7.3561742901802098E-3</v>
-      </c>
-      <c r="F4">
-        <v>0.423814177513123</v>
-      </c>
-      <c r="G4">
-        <v>1.4</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>7.4092089198529699E-4</v>
-      </c>
-      <c r="B5">
-        <v>-0.14775538444519001</v>
-      </c>
-      <c r="C5">
-        <v>3.4220633096993E-3</v>
-      </c>
-      <c r="D5">
-        <v>-0.161362335085869</v>
-      </c>
-      <c r="E5">
-        <v>2.0262047648429898E-2</v>
-      </c>
-      <c r="F5">
-        <v>0.82944488525390603</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>6.6551081836223602E-3</v>
-      </c>
-      <c r="B6">
-        <v>-0.148307904601097</v>
-      </c>
-      <c r="C6">
-        <v>-1.0527462000027299E-3</v>
-      </c>
-      <c r="D6">
-        <v>-0.444706320762634</v>
-      </c>
-      <c r="E6">
-        <v>-2.19946205615997E-2</v>
-      </c>
-      <c r="F6">
-        <v>0.489793181419373</v>
-      </c>
-      <c r="G6">
-        <v>1.4</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>8.7637116666883198E-4</v>
-      </c>
-      <c r="B7">
-        <v>-0.164488449692726</v>
-      </c>
-      <c r="C7">
-        <v>3.7763002328574701E-3</v>
-      </c>
-      <c r="D7">
-        <v>-0.58729076385498002</v>
-      </c>
-      <c r="E7">
-        <v>7.8071318566799199E-3</v>
-      </c>
-      <c r="F7">
-        <v>0.38755592703819303</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>-8.6323916912078901E-4</v>
-      </c>
-      <c r="B8">
-        <v>4.2902048677205998E-2</v>
-      </c>
-      <c r="C8">
-        <v>-8.0319754779338795E-2</v>
-      </c>
-      <c r="D8">
-        <v>0.61245459318161</v>
-      </c>
-      <c r="E8">
-        <v>-0.54026973247528098</v>
-      </c>
-      <c r="F8">
-        <v>-0.28817486763000499</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>-8.0120982602238698E-4</v>
-      </c>
-      <c r="B9">
-        <v>4.2666438966989503E-2</v>
-      </c>
-      <c r="C9">
-        <v>-8.0293677747249603E-2</v>
-      </c>
-      <c r="D9">
-        <v>0.443310797214508</v>
-      </c>
-      <c r="E9">
-        <v>-0.42717015743255599</v>
-      </c>
-      <c r="F9">
-        <v>-0.22529536485672</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>-5.5334065109491301E-5</v>
-      </c>
-      <c r="B10">
-        <v>7.7956624329090105E-2</v>
-      </c>
-      <c r="C10">
-        <v>-0.13737398386001601</v>
-      </c>
-      <c r="D10">
-        <v>0.41918036341667197</v>
-      </c>
-      <c r="E10">
-        <v>-0.55125319957733199</v>
-      </c>
-      <c r="F10">
-        <v>-0.30630308389663702</v>
-      </c>
-      <c r="G10">
-        <v>1.4</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>-9.6024014055728899E-5</v>
-      </c>
-      <c r="B11">
-        <v>3.4424368292093298E-2</v>
-      </c>
-      <c r="C11">
-        <v>-6.16564750671387E-2</v>
-      </c>
-      <c r="D11">
-        <v>0.267098218202591</v>
-      </c>
-      <c r="E11">
-        <v>-0.21448078751564001</v>
-      </c>
-      <c r="F11">
-        <v>-0.115060687065125</v>
-      </c>
-      <c r="G11">
-        <v>1.4</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>-3.7108035758137698E-4</v>
-      </c>
-      <c r="B12">
-        <v>3.7644270807504703E-2</v>
-      </c>
-      <c r="C12">
-        <v>-6.73996657133102E-2</v>
-      </c>
-      <c r="D12">
-        <v>1.67829748243093E-2</v>
-      </c>
-      <c r="E12">
-        <v>-0.33880779147148099</v>
-      </c>
-      <c r="F12">
-        <v>-0.185297966003418</v>
-      </c>
-      <c r="G12">
-        <v>1.4</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>-1.02429185062647E-3</v>
-      </c>
-      <c r="B13">
-        <v>7.0613205432891804E-2</v>
-      </c>
-      <c r="C13">
-        <v>-0.12678831815719599</v>
-      </c>
-      <c r="D13">
-        <v>-2.9671346768736801E-2</v>
-      </c>
-      <c r="E13">
-        <v>-0.63574087619781505</v>
-      </c>
-      <c r="F13">
-        <v>-0.34651768207549999</v>
-      </c>
-      <c r="G13">
-        <v>1.4</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>-6.0879066586494402E-4</v>
-      </c>
-      <c r="B14">
-        <v>4.7145899385213901E-2</v>
-      </c>
-      <c r="C14">
-        <v>-8.5028916597366305E-2</v>
-      </c>
-      <c r="D14">
-        <v>-7.4065491557121305E-2</v>
-      </c>
-      <c r="E14">
-        <v>-0.31546109914779702</v>
-      </c>
-      <c r="F14">
-        <v>-0.17043319344520599</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>3.8368394598364803E-5</v>
-      </c>
-      <c r="B15">
-        <v>3.2897148281335803E-2</v>
-      </c>
-      <c r="C15">
-        <v>-5.8571800589561497E-2</v>
-      </c>
-      <c r="D15">
-        <v>-6.3505612313747406E-2</v>
-      </c>
-      <c r="E15">
-        <v>-0.19738522171974199</v>
-      </c>
-      <c r="F15">
-        <v>-0.108248926699162</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D6F75F-00D5-499A-8B94-C01DFDD9DEC2}">
   <dimension ref="A1:Z17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" customWidth="1"/>
-    <col min="23" max="23" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.5703125" customWidth="1"/>
+    <col min="19" max="19" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7265625" customWidth="1"/>
+    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="24" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="22" t="s">
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="25" t="s">
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
       <c r="V1" s="6"/>
-      <c r="W1" s="23" t="s">
+      <c r="W1" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-    </row>
-    <row r="2" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2748,7 +2304,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
         <f>'Proximal Validation (single)'!A3</f>
         <v>0.3</v>
@@ -2849,7 +2405,7 @@
         <v>8.5712786606328514E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <f>'Proximal Validation (single)'!A4</f>
         <v>0.4</v>
@@ -2942,7 +2498,7 @@
         <v>4.9109809228480739</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <f>'Proximal Validation (single)'!A5</f>
         <v>0.6</v>
@@ -3027,7 +2583,7 @@
         <v>4.1599788529260939E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <f>'Proximal Validation (single)'!A6</f>
         <v>0.4</v>
@@ -3112,7 +2668,7 @@
         <v>4.2221659829549951E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <f>'Proximal Validation (single)'!A7</f>
         <v>0.8</v>
@@ -3197,7 +2753,7 @@
         <v>6.6669824716722559E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <f>'Proximal Validation (single)'!A8</f>
         <v>0.7</v>
@@ -3282,7 +2838,7 @@
         <v>0.14193965592537872</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <f>'Proximal Validation (single)'!A9</f>
         <v>0.7</v>
@@ -3367,7 +2923,7 @@
         <v>0.24772059968584892</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <f>'Proximal Validation (single)'!A10</f>
         <v>0.7</v>
@@ -3452,7 +3008,7 @@
         <v>3.7860114207274531E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <f>'Proximal Validation (single)'!A11</f>
         <v>0.6</v>
@@ -3537,7 +3093,7 @@
         <v>5.7967262912724249E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <f>'Proximal Validation (single)'!A12</f>
         <v>0.8</v>
@@ -3622,7 +3178,7 @@
         <v>0.14817324795315401</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <f>'Proximal Validation (single)'!A13</f>
         <v>0.4</v>
@@ -3707,7 +3263,7 @@
         <v>0.10886515822791509</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <f>'Proximal Validation (single)'!A14</f>
         <v>0.4</v>
@@ -3792,7 +3348,7 @@
         <v>8.1105897328739074E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <f>'Proximal Validation (single)'!A15</f>
         <v>0.7</v>
@@ -3877,7 +3433,7 @@
         <v>8.4660428579046876E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <f>'Proximal Validation (single)'!A16</f>
         <v>0.4</v>
@@ -3962,7 +3518,7 @@
         <v>0.11197227303643653</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <f>'Proximal Validation (single)'!A17</f>
         <v>0.3</v>
@@ -4060,69 +3616,69 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C7F774-9DF3-4E6E-BB0A-FE0B8E71539C}">
   <dimension ref="A1:Z17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" customWidth="1"/>
-    <col min="23" max="23" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.5703125" customWidth="1"/>
+    <col min="19" max="19" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7265625" customWidth="1"/>
+    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="24" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="22" t="s">
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="25" t="s">
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
       <c r="V1" s="6"/>
-      <c r="W1" s="23" t="s">
+      <c r="W1" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-    </row>
-    <row r="2" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -4202,7 +3758,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
         <f>'Proximal Validation (single)'!A3</f>
         <v>0.3</v>
@@ -4255,45 +3811,55 @@
         <f>'Proximal Validation (single)'!M3</f>
         <v>0.19288232922553999</v>
       </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="10"/>
+      <c r="N3" s="9">
+        <v>0.24504740208502601</v>
+      </c>
+      <c r="O3" s="9">
+        <v>7.7275782510532201E-2</v>
+      </c>
+      <c r="P3" s="9">
+        <v>1.5885960085949349</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>0.91200086849673101</v>
+      </c>
+      <c r="R3" s="10">
+        <v>9.8072138645546656E-8</v>
+      </c>
       <c r="S3" s="8">
         <f>ABS(N3-A3)</f>
-        <v>0.3</v>
+        <v>5.4952597914973977E-2</v>
       </c>
       <c r="T3" s="8">
         <f t="shared" ref="T3:V17" si="0">ABS(O3-B3)</f>
-        <v>0.08</v>
+        <v>2.7242174894678006E-3</v>
       </c>
       <c r="U3" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>1.7596008594934931E-2</v>
       </c>
       <c r="V3" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
+        <v>0.12700086849673098</v>
       </c>
       <c r="W3" s="9">
         <f>AVERAGE(S3:S17)</f>
-        <v>0.54666666666666675</v>
+        <v>5.2799358760934625E-2</v>
       </c>
       <c r="X3" s="9">
         <f t="shared" ref="X3:Z3" si="1">AVERAGE(T3:T17)</f>
-        <v>0.13066666666666668</v>
+        <v>3.7109417622652331E-2</v>
       </c>
       <c r="Y3" s="9">
         <f>AVERAGE(U3:U17)</f>
-        <v>2.6877999999999997</v>
+        <v>2.5826122106533751E-2</v>
       </c>
       <c r="Z3" s="9">
         <f t="shared" si="1"/>
-        <v>1.2042000000000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.10208435606763017</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <f>'Proximal Validation (single)'!A4</f>
         <v>0.4</v>
@@ -4346,37 +3912,47 @@
         <f>'Proximal Validation (single)'!M4</f>
         <v>0.27653545141220098</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="10"/>
+      <c r="N4" s="9">
+        <v>0.34565730479478768</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0.1355779527649357</v>
+      </c>
+      <c r="P4" s="9">
+        <v>1.5327313989207005</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>0.86389873279400697</v>
+      </c>
+      <c r="R4" s="10">
+        <v>6.8609497671031312E-7</v>
+      </c>
       <c r="S4" s="8">
         <f t="shared" ref="S4:S17" si="2">ABS(N4-A4)</f>
-        <v>0.4</v>
+        <v>5.4342695205212344E-2</v>
       </c>
       <c r="T4" s="8">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>4.4220472350643136E-3</v>
       </c>
       <c r="U4" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>3.8268601079299414E-2</v>
       </c>
       <c r="V4" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
+        <v>7.8898732794006943E-2</v>
       </c>
       <c r="Y4">
         <f>DEGREES(Y3)</f>
-        <v>153.99959617526267</v>
+        <v>1.479727797893899</v>
       </c>
       <c r="Z4">
         <f>DEGREES(Z3)</f>
-        <v>68.995577689653743</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+        <v>5.849002756985926</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <f>'Proximal Validation (single)'!A5</f>
         <v>0.6</v>
@@ -4429,29 +4005,39 @@
         <f>'Proximal Validation (single)'!M5</f>
         <v>0.52633810043335005</v>
       </c>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="10"/>
+      <c r="N5" s="9">
+        <v>0.58260936985982126</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0.14867087839664922</v>
+      </c>
+      <c r="P5" s="9">
+        <v>1.6735150528462999</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0.90959001517049765</v>
+      </c>
+      <c r="R5" s="10">
+        <v>2.2743475928177483E-6</v>
+      </c>
       <c r="S5" s="8">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>1.739063014017872E-2</v>
       </c>
       <c r="T5" s="8">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>1.1329121603350784E-2</v>
       </c>
       <c r="U5" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>0.10251505284629991</v>
       </c>
       <c r="V5" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.12459001517049761</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <f>'Proximal Validation (single)'!A6</f>
         <v>0.4</v>
@@ -4504,29 +4090,39 @@
         <f>'Proximal Validation (single)'!M6</f>
         <v>0.423814177513123</v>
       </c>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="10"/>
+      <c r="N6" s="9">
+        <v>0.43977206766596794</v>
+      </c>
+      <c r="O6" s="9">
+        <v>6.2954012505445217E-2</v>
+      </c>
+      <c r="P6" s="9">
+        <v>1.5525836590126203</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>1.5943229048732539</v>
+      </c>
+      <c r="R6" s="10">
+        <v>4.0141733003867427E-8</v>
+      </c>
       <c r="S6" s="8">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>3.9772067665967914E-2</v>
       </c>
       <c r="T6" s="8">
         <f t="shared" si="0"/>
-        <v>0.06</v>
+        <v>2.9540125054452193E-3</v>
       </c>
       <c r="U6" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>1.8416340987379654E-2</v>
       </c>
       <c r="V6" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2.3322904873253947E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <f>'Proximal Validation (single)'!A7</f>
         <v>0.8</v>
@@ -4579,29 +4175,39 @@
         <f>'Proximal Validation (single)'!M7</f>
         <v>0.82944488525390603</v>
       </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="10"/>
+      <c r="N7" s="9">
+        <v>0.86756768113535498</v>
+      </c>
+      <c r="O7" s="9">
+        <v>8.2375239550059612E-2</v>
+      </c>
+      <c r="P7" s="9">
+        <v>1.546757049905189</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>1.6005686329816045</v>
+      </c>
+      <c r="R7" s="10">
+        <v>2.2863636619140079E-6</v>
+      </c>
       <c r="S7" s="8">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>6.756768113535494E-2</v>
       </c>
       <c r="T7" s="8">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>2.3752395500596102E-3</v>
       </c>
       <c r="U7" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>2.4242950094810922E-2</v>
       </c>
       <c r="V7" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2.9568632981604503E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <f>'Proximal Validation (single)'!A8</f>
         <v>0.7</v>
@@ -4654,29 +4260,39 @@
         <f>'Proximal Validation (single)'!M8</f>
         <v>0.489793181419373</v>
       </c>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="10"/>
+      <c r="N8" s="9">
+        <v>0.61084967694221104</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0.17837063238150705</v>
+      </c>
+      <c r="P8" s="9">
+        <v>1.5850017257491844</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>1.5668304861069597</v>
+      </c>
+      <c r="R8" s="10">
+        <v>7.3150947194322727E-6</v>
+      </c>
       <c r="S8" s="8">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>8.9150323057788916E-2</v>
       </c>
       <c r="T8" s="8">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>1.8370632381507046E-2</v>
       </c>
       <c r="U8" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>1.4001725749184457E-2</v>
       </c>
       <c r="V8" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.1695138930402109E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <f>'Proximal Validation (single)'!A9</f>
         <v>0.7</v>
@@ -4729,29 +4345,39 @@
         <f>'Proximal Validation (single)'!M9</f>
         <v>0.38755592703819303</v>
       </c>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="10"/>
+      <c r="N9" s="9">
+        <v>0.60840835934457149</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="P9" s="9">
+        <v>1.5514507810741749</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>1.7506262400245944</v>
+      </c>
+      <c r="R9" s="10">
+        <v>6.2562187844172521E-4</v>
+      </c>
       <c r="S9" s="8">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>9.1591640655428463E-2</v>
       </c>
       <c r="T9" s="8">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="U9" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>1.9549218925825063E-2</v>
       </c>
       <c r="V9" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.17962624002459449</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <f>'Proximal Validation (single)'!A10</f>
         <v>0.7</v>
@@ -4804,29 +4430,39 @@
         <f>'Proximal Validation (single)'!M10</f>
         <v>-0.28817486763000499</v>
       </c>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="10"/>
+      <c r="N10" s="9">
+        <v>0.78642387084970899</v>
+      </c>
+      <c r="O10" s="9">
+        <v>1.3740633079946964E-2</v>
+      </c>
+      <c r="P10" s="9">
+        <v>3.6355470514505059</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0.93162572086260642</v>
+      </c>
+      <c r="R10" s="10">
+        <v>2.0040264277590834E-4</v>
+      </c>
       <c r="S10" s="8">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>8.6423870849709039E-2</v>
       </c>
       <c r="T10" s="8">
         <f t="shared" si="0"/>
-        <v>0.06</v>
+        <v>4.625936692005303E-2</v>
       </c>
       <c r="U10" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>2.9452948549494096E-2</v>
       </c>
       <c r="V10" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.14662572086260639</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <f>'Proximal Validation (single)'!A11</f>
         <v>0.6</v>
@@ -4879,29 +4515,39 @@
         <f>'Proximal Validation (single)'!M11</f>
         <v>-0.22529536485672</v>
       </c>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="10"/>
+      <c r="N11" s="9">
+        <v>0.60265161871706618</v>
+      </c>
+      <c r="O11" s="9">
+        <v>4.0170224106255634E-2</v>
+      </c>
+      <c r="P11" s="9">
+        <v>3.6322534102610673</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0.95994291648098384</v>
+      </c>
+      <c r="R11" s="10">
+        <v>2.0196310696216706E-4</v>
+      </c>
       <c r="S11" s="8">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>2.6516187170662064E-3</v>
       </c>
       <c r="T11" s="8">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>5.9829775893744372E-2</v>
       </c>
       <c r="U11" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>3.2746589738932741E-2</v>
       </c>
       <c r="V11" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.17494291648098381</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <f>'Proximal Validation (single)'!A12</f>
         <v>0.8</v>
@@ -4954,29 +4600,39 @@
         <f>'Proximal Validation (single)'!M12</f>
         <v>-0.30630308389663702</v>
       </c>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="10"/>
+      <c r="N12" s="9">
+        <v>0.72536661002451797</v>
+      </c>
+      <c r="O12" s="9">
+        <v>8.6323039496506271E-2</v>
+      </c>
+      <c r="P12" s="9">
+        <v>3.6574989426539486</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>1.0637681195562441</v>
+      </c>
+      <c r="R12" s="10">
+        <v>6.7783135342438258E-4</v>
+      </c>
       <c r="S12" s="8">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>7.4633389975482078E-2</v>
       </c>
       <c r="T12" s="8">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>9.3676960503493722E-2</v>
       </c>
       <c r="U12" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>7.5010573460514429E-3</v>
       </c>
       <c r="V12" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.27876811955624403</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <f>'Proximal Validation (single)'!A13</f>
         <v>0.4</v>
@@ -5029,29 +4685,39 @@
         <f>'Proximal Validation (single)'!M13</f>
         <v>-0.115060687065125</v>
       </c>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="10"/>
+      <c r="N13" s="9">
+        <v>0.32368931001065393</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0.11266706442832367</v>
+      </c>
+      <c r="P13" s="9">
+        <v>3.6459217943233444</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0.8845361130076389</v>
+      </c>
+      <c r="R13" s="10">
+        <v>1.4083545408800932E-4</v>
+      </c>
       <c r="S13" s="8">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>7.6310689989346092E-2</v>
       </c>
       <c r="T13" s="8">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>8.7332935571676346E-2</v>
       </c>
       <c r="U13" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>1.9078205676655635E-2</v>
       </c>
       <c r="V13" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+        <v>9.9536113007638871E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <f>'Proximal Validation (single)'!A14</f>
         <v>0.4</v>
@@ -5104,29 +4770,39 @@
         <f>'Proximal Validation (single)'!M14</f>
         <v>-0.185297966003418</v>
       </c>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="10"/>
+      <c r="N14" s="9">
+        <v>0.39866490904146223</v>
+      </c>
+      <c r="O14" s="9">
+        <v>4.9020881530599851E-2</v>
+      </c>
+      <c r="P14" s="9">
+        <v>3.6481432226433044</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>1.5427970208007731</v>
+      </c>
+      <c r="R14" s="10">
+        <v>1.6104946929566442E-4</v>
+      </c>
       <c r="S14" s="8">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>1.3350909585377879E-3</v>
       </c>
       <c r="T14" s="8">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>5.0979118469400155E-2</v>
       </c>
       <c r="U14" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>1.6856777356695662E-2</v>
       </c>
       <c r="V14" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2.8202979199226874E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <f>'Proximal Validation (single)'!A15</f>
         <v>0.7</v>
@@ -5179,29 +4855,39 @@
         <f>'Proximal Validation (single)'!M15</f>
         <v>-0.34651768207549999</v>
       </c>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="10"/>
+      <c r="N15" s="9">
+        <v>0.74742798273338096</v>
+      </c>
+      <c r="O15" s="9">
+        <v>4.9289600658586979E-2</v>
+      </c>
+      <c r="P15" s="9">
+        <v>3.6467145109350931</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>1.5907300908532844</v>
+      </c>
+      <c r="R15" s="10">
+        <v>5.6873202205466502E-4</v>
+      </c>
       <c r="S15" s="8">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>4.7427982733381002E-2</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>5.0710399341413026E-2</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>1.8285489064906901E-2</v>
       </c>
       <c r="V15" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1.9730090853284477E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <f>'Proximal Validation (single)'!A16</f>
         <v>0.4</v>
@@ -5254,29 +4940,39 @@
         <f>'Proximal Validation (single)'!M16</f>
         <v>-0.17043319344520599</v>
       </c>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="10"/>
+      <c r="N16" s="9">
+        <v>0.37426267958076559</v>
+      </c>
+      <c r="O16" s="9">
+        <v>9.7592333579262364E-2</v>
+      </c>
+      <c r="P16" s="9">
+        <v>3.6465759570878129</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>1.6504719135950212</v>
+      </c>
+      <c r="R16" s="10">
+        <v>2.5407515657104577E-4</v>
+      </c>
       <c r="S16" s="8">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>2.5737320419234433E-2</v>
       </c>
       <c r="T16" s="8">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>6.240766642073764E-2</v>
       </c>
       <c r="U16" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>1.8424042912187133E-2</v>
       </c>
       <c r="V16" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+        <v>7.947191359502126E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <f>'Proximal Validation (single)'!A17</f>
         <v>0.3</v>
@@ -5329,26 +5025,1490 @@
         <f>'Proximal Validation (single)'!M17</f>
         <v>-0.108248926699162</v>
       </c>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="10"/>
+      <c r="N17" s="9">
+        <v>0.23729721800364259</v>
+      </c>
+      <c r="O17" s="9">
+        <v>0.11673022954562813</v>
+      </c>
+      <c r="P17" s="9">
+        <v>3.6545431773246517</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>1.7078105792257181</v>
+      </c>
+      <c r="R17" s="10">
+        <v>1.2108671225991037E-4</v>
+      </c>
       <c r="S17" s="8">
         <f t="shared" si="2"/>
+        <v>6.2702781996357398E-2</v>
+      </c>
+      <c r="T17" s="8">
+        <f t="shared" si="0"/>
+        <v>6.3269770454371863E-2</v>
+      </c>
+      <c r="U17" s="8">
+        <f t="shared" si="0"/>
+        <v>1.045682267534831E-2</v>
+      </c>
+      <c r="V17" s="8">
+        <f t="shared" si="0"/>
+        <v>0.13681057922571815</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:R1"/>
+    <mergeCell ref="S1:U1"/>
+    <mergeCell ref="W1:Y1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4F90B31-7E83-47D4-ACA7-98FCDDCC330D}">
+  <dimension ref="A1:Z17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="19" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7265625" customWidth="1"/>
+    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A3" s="9">
+        <f>'Proximal Validation (single)'!A3</f>
         <v>0.3</v>
       </c>
+      <c r="B3" s="9">
+        <f>'Proximal Validation (single)'!B3</f>
+        <v>0.08</v>
+      </c>
+      <c r="C3" s="9">
+        <f>'Proximal Validation (single)'!C3</f>
+        <v>1.571</v>
+      </c>
+      <c r="D3" s="9">
+        <f>'Proximal Validation (single)'!D3</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E3" s="9">
+        <f>'Proximal Validation (single)'!E3</f>
+        <v>1.4</v>
+      </c>
+      <c r="F3" s="9">
+        <f>'Proximal Validation (single)'!F3</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="9">
+        <f>'Proximal Validation (single)'!G3</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="9">
+        <f>'Proximal Validation (single)'!H3</f>
+        <v>2.6342464843764901E-4</v>
+      </c>
+      <c r="I3" s="9">
+        <f>'Proximal Validation (single)'!I3</f>
+        <v>-3.2978262752294499E-2</v>
+      </c>
+      <c r="J3" s="9">
+        <f>'Proximal Validation (single)'!J3</f>
+        <v>5.6162860710173802E-4</v>
+      </c>
+      <c r="K3" s="9">
+        <f>'Proximal Validation (single)'!K3</f>
+        <v>0.185834720730782</v>
+      </c>
+      <c r="L3" s="9">
+        <f>'Proximal Validation (single)'!L3</f>
+        <v>1.13257020711899E-3</v>
+      </c>
+      <c r="M3" s="9">
+        <f>'Proximal Validation (single)'!M3</f>
+        <v>0.19288232922553999</v>
+      </c>
+      <c r="N3" s="9">
+        <v>0.22176367606154754</v>
+      </c>
+      <c r="O3" s="9">
+        <v>5.9342310880851477E-2</v>
+      </c>
+      <c r="P3" s="9">
+        <v>1.513808342273647</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>1.2309282130873864</v>
+      </c>
+      <c r="R3" s="10">
+        <v>5.0828320559270182E-4</v>
+      </c>
+      <c r="S3" s="8">
+        <f>ABS(N3-A3)</f>
+        <v>7.8236323938452451E-2</v>
+      </c>
+      <c r="T3" s="8">
+        <f t="shared" ref="T3:V17" si="0">ABS(O3-B3)</f>
+        <v>2.0657689119148524E-2</v>
+      </c>
+      <c r="U3" s="8">
+        <f t="shared" si="0"/>
+        <v>5.7191657726352929E-2</v>
+      </c>
+      <c r="V3" s="8">
+        <f t="shared" si="0"/>
+        <v>0.44592821308738639</v>
+      </c>
+      <c r="W3" s="9">
+        <f>AVERAGE(S3:S17)</f>
+        <v>6.2980744945213121E-2</v>
+      </c>
+      <c r="X3" s="9">
+        <f t="shared" ref="X3:Z3" si="1">AVERAGE(T3:T17)</f>
+        <v>2.3217298004290361E-2</v>
+      </c>
+      <c r="Y3" s="9">
+        <f>AVERAGE(U3:U17)</f>
+        <v>5.1852619629878451E-2</v>
+      </c>
+      <c r="Z3" s="9">
+        <f t="shared" si="1"/>
+        <v>0.1984507285588433</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A4" s="9">
+        <f>'Proximal Validation (single)'!A4</f>
+        <v>0.4</v>
+      </c>
+      <c r="B4" s="9">
+        <f>'Proximal Validation (single)'!B4</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C4" s="9">
+        <f>'Proximal Validation (single)'!C4</f>
+        <v>1.571</v>
+      </c>
+      <c r="D4" s="9">
+        <f>'Proximal Validation (single)'!D4</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E4" s="9">
+        <f>'Proximal Validation (single)'!E4</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="9">
+        <f>'Proximal Validation (single)'!F4</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="9">
+        <f>'Proximal Validation (single)'!G4</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="9">
+        <f>'Proximal Validation (single)'!H4</f>
+        <v>-4.3474312406033299E-4</v>
+      </c>
+      <c r="I4" s="9">
+        <f>'Proximal Validation (single)'!I4</f>
+        <v>-6.2425632029771798E-2</v>
+      </c>
+      <c r="J4" s="9">
+        <f>'Proximal Validation (single)'!J4</f>
+        <v>2.5845002382993698E-3</v>
+      </c>
+      <c r="K4" s="9">
+        <f>'Proximal Validation (single)'!K4</f>
+        <v>0.25303724408149703</v>
+      </c>
+      <c r="L4" s="9">
+        <f>'Proximal Validation (single)'!L4</f>
+        <v>1.07369087636471E-2</v>
+      </c>
+      <c r="M4" s="9">
+        <f>'Proximal Validation (single)'!M4</f>
+        <v>0.27653545141220098</v>
+      </c>
+      <c r="N4" s="9">
+        <v>0.32473144116695835</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0.11909644178987432</v>
+      </c>
+      <c r="P4" s="9">
+        <v>1.4964085929957633</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>1.0529363037610366</v>
+      </c>
+      <c r="R4" s="10">
+        <v>5.5022249700236207E-4</v>
+      </c>
+      <c r="S4" s="8">
+        <f t="shared" ref="S4:S17" si="2">ABS(N4-A4)</f>
+        <v>7.5268558833041677E-2</v>
+      </c>
+      <c r="T4" s="8">
+        <f t="shared" si="0"/>
+        <v>2.0903558210125697E-2</v>
+      </c>
+      <c r="U4" s="8">
+        <f t="shared" si="0"/>
+        <v>7.459140700423661E-2</v>
+      </c>
+      <c r="V4" s="8">
+        <f t="shared" si="0"/>
+        <v>0.26793630376103661</v>
+      </c>
+      <c r="Y4">
+        <f>DEGREES(Y3)</f>
+        <v>2.9709362614892401</v>
+      </c>
+      <c r="Z4">
+        <f>DEGREES(Z3)</f>
+        <v>11.370389187718034</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A5" s="9">
+        <f>'Proximal Validation (single)'!A5</f>
+        <v>0.6</v>
+      </c>
+      <c r="B5" s="9">
+        <f>'Proximal Validation (single)'!B5</f>
+        <v>0.16</v>
+      </c>
+      <c r="C5" s="9">
+        <f>'Proximal Validation (single)'!C5</f>
+        <v>1.571</v>
+      </c>
+      <c r="D5" s="9">
+        <f>'Proximal Validation (single)'!D5</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E5" s="9">
+        <f>'Proximal Validation (single)'!E5</f>
+        <v>1.4</v>
+      </c>
+      <c r="F5" s="9">
+        <f>'Proximal Validation (single)'!F5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="9">
+        <f>'Proximal Validation (single)'!G5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="9">
+        <f>'Proximal Validation (single)'!H5</f>
+        <v>5.3234044462442398E-3</v>
+      </c>
+      <c r="I5" s="9">
+        <f>'Proximal Validation (single)'!I5</f>
+        <v>-0.12275674194097499</v>
+      </c>
+      <c r="J5" s="9">
+        <f>'Proximal Validation (single)'!J5</f>
+        <v>-8.3989212289452605E-3</v>
+      </c>
+      <c r="K5" s="9">
+        <f>'Proximal Validation (single)'!K5</f>
+        <v>0.26806160807609603</v>
+      </c>
+      <c r="L5" s="9">
+        <f>'Proximal Validation (single)'!L5</f>
+        <v>-2.4467468261718799E-2</v>
+      </c>
+      <c r="M5" s="9">
+        <f>'Proximal Validation (single)'!M5</f>
+        <v>0.52633810043335005</v>
+      </c>
+      <c r="N5" s="9">
+        <v>0.56432391300692308</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0.14565947353953146</v>
+      </c>
+      <c r="P5" s="9">
+        <v>1.640723280152844</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>1.0056209109917909</v>
+      </c>
+      <c r="R5" s="10">
+        <v>6.1233044375456718E-4</v>
+      </c>
+      <c r="S5" s="8">
+        <f t="shared" si="2"/>
+        <v>3.5676086993076894E-2</v>
+      </c>
+      <c r="T5" s="8">
+        <f t="shared" si="0"/>
+        <v>1.4340526460468545E-2</v>
+      </c>
+      <c r="U5" s="8">
+        <f t="shared" si="0"/>
+        <v>6.9723280152844014E-2</v>
+      </c>
+      <c r="V5" s="8">
+        <f t="shared" si="0"/>
+        <v>0.22062091099179082</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A6" s="9">
+        <f>'Proximal Validation (single)'!A6</f>
+        <v>0.4</v>
+      </c>
+      <c r="B6" s="9">
+        <f>'Proximal Validation (single)'!B6</f>
+        <v>0.06</v>
+      </c>
+      <c r="C6" s="9">
+        <f>'Proximal Validation (single)'!C6</f>
+        <v>1.571</v>
+      </c>
+      <c r="D6" s="9">
+        <f>'Proximal Validation (single)'!D6</f>
+        <v>1.571</v>
+      </c>
+      <c r="E6" s="9">
+        <f>'Proximal Validation (single)'!E6</f>
+        <v>1.4</v>
+      </c>
+      <c r="F6" s="9">
+        <f>'Proximal Validation (single)'!F6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <f>'Proximal Validation (single)'!G6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <f>'Proximal Validation (single)'!H6</f>
+        <v>6.7002582363784302E-4</v>
+      </c>
+      <c r="I6" s="9">
+        <f>'Proximal Validation (single)'!I6</f>
+        <v>-6.6750191152095795E-2</v>
+      </c>
+      <c r="J6" s="9">
+        <f>'Proximal Validation (single)'!J6</f>
+        <v>1.6002767952158999E-3</v>
+      </c>
+      <c r="K6" s="9">
+        <f>'Proximal Validation (single)'!K6</f>
+        <v>-3.97013984620571E-2</v>
+      </c>
+      <c r="L6" s="9">
+        <f>'Proximal Validation (single)'!L6</f>
+        <v>7.3561742901802098E-3</v>
+      </c>
+      <c r="M6" s="9">
+        <f>'Proximal Validation (single)'!M6</f>
+        <v>0.423814177513123</v>
+      </c>
+      <c r="N6" s="9">
+        <v>0.46913480662901258</v>
+      </c>
+      <c r="O6" s="9">
+        <v>5.7488786909511924E-2</v>
+      </c>
+      <c r="P6" s="9">
+        <v>1.5189214557901527</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>1.8734235241211525</v>
+      </c>
+      <c r="R6" s="10">
+        <v>5.0230758024864645E-4</v>
+      </c>
+      <c r="S6" s="8">
+        <f t="shared" si="2"/>
+        <v>6.9134806629012557E-2</v>
+      </c>
+      <c r="T6" s="8">
+        <f t="shared" si="0"/>
+        <v>2.5112130904880736E-3</v>
+      </c>
+      <c r="U6" s="8">
+        <f t="shared" si="0"/>
+        <v>5.2078544209847255E-2</v>
+      </c>
+      <c r="V6" s="8">
+        <f t="shared" si="0"/>
+        <v>0.30242352412115259</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A7" s="9">
+        <f>'Proximal Validation (single)'!A7</f>
+        <v>0.8</v>
+      </c>
+      <c r="B7" s="9">
+        <f>'Proximal Validation (single)'!B7</f>
+        <v>0.08</v>
+      </c>
+      <c r="C7" s="9">
+        <f>'Proximal Validation (single)'!C7</f>
+        <v>1.571</v>
+      </c>
+      <c r="D7" s="9">
+        <f>'Proximal Validation (single)'!D7</f>
+        <v>1.571</v>
+      </c>
+      <c r="E7" s="9">
+        <f>'Proximal Validation (single)'!E7</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <f>'Proximal Validation (single)'!F7</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <f>'Proximal Validation (single)'!G7</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <f>'Proximal Validation (single)'!H7</f>
+        <v>7.4092089198529699E-4</v>
+      </c>
+      <c r="I7" s="9">
+        <f>'Proximal Validation (single)'!I7</f>
+        <v>-0.14775538444519001</v>
+      </c>
+      <c r="J7" s="9">
+        <f>'Proximal Validation (single)'!J7</f>
+        <v>3.4220633096993E-3</v>
+      </c>
+      <c r="K7" s="9">
+        <f>'Proximal Validation (single)'!K7</f>
+        <v>-0.161362335085869</v>
+      </c>
+      <c r="L7" s="9">
+        <f>'Proximal Validation (single)'!L7</f>
+        <v>2.0262047648429898E-2</v>
+      </c>
+      <c r="M7" s="9">
+        <f>'Proximal Validation (single)'!M7</f>
+        <v>0.82944488525390603</v>
+      </c>
+      <c r="N7" s="9">
+        <v>0.89244981573469562</v>
+      </c>
+      <c r="O7" s="9">
+        <v>8.1642191216504886E-2</v>
+      </c>
+      <c r="P7" s="9">
+        <v>1.5329171355725022</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>1.7778875069926667</v>
+      </c>
+      <c r="R7" s="10">
+        <v>5.2889552060216667E-4</v>
+      </c>
+      <c r="S7" s="8">
+        <f t="shared" si="2"/>
+        <v>9.2449815734695573E-2</v>
+      </c>
+      <c r="T7" s="8">
+        <f t="shared" si="0"/>
+        <v>1.6421912165048846E-3</v>
+      </c>
+      <c r="U7" s="8">
+        <f t="shared" si="0"/>
+        <v>3.8082864427497753E-2</v>
+      </c>
+      <c r="V7" s="8">
+        <f t="shared" si="0"/>
+        <v>0.20688750699266678</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A8" s="9">
+        <f>'Proximal Validation (single)'!A8</f>
+        <v>0.7</v>
+      </c>
+      <c r="B8" s="9">
+        <f>'Proximal Validation (single)'!B8</f>
+        <v>0.16</v>
+      </c>
+      <c r="C8" s="9">
+        <f>'Proximal Validation (single)'!C8</f>
+        <v>1.571</v>
+      </c>
+      <c r="D8" s="9">
+        <f>'Proximal Validation (single)'!D8</f>
+        <v>1.571</v>
+      </c>
+      <c r="E8" s="9">
+        <f>'Proximal Validation (single)'!E8</f>
+        <v>1.4</v>
+      </c>
+      <c r="F8" s="9">
+        <f>'Proximal Validation (single)'!F8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <f>'Proximal Validation (single)'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <f>'Proximal Validation (single)'!H8</f>
+        <v>6.6551081836223602E-3</v>
+      </c>
+      <c r="I8" s="9">
+        <f>'Proximal Validation (single)'!I8</f>
+        <v>-0.148307904601097</v>
+      </c>
+      <c r="J8" s="9">
+        <f>'Proximal Validation (single)'!J8</f>
+        <v>-1.0527462000027299E-3</v>
+      </c>
+      <c r="K8" s="9">
+        <f>'Proximal Validation (single)'!K8</f>
+        <v>-0.444706320762634</v>
+      </c>
+      <c r="L8" s="9">
+        <f>'Proximal Validation (single)'!L8</f>
+        <v>-2.19946205615997E-2</v>
+      </c>
+      <c r="M8" s="9">
+        <f>'Proximal Validation (single)'!M8</f>
+        <v>0.489793181419373</v>
+      </c>
+      <c r="N8" s="9">
+        <v>0.75780333298527358</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0.15872145562222162</v>
+      </c>
+      <c r="P8" s="9">
+        <v>1.5293918377324254</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>1.9203804414133436</v>
+      </c>
+      <c r="R8" s="10">
+        <v>5.1832878781188948E-4</v>
+      </c>
+      <c r="S8" s="8">
+        <f t="shared" si="2"/>
+        <v>5.7803332985273626E-2</v>
+      </c>
+      <c r="T8" s="8">
+        <f t="shared" si="0"/>
+        <v>1.2785443777783845E-3</v>
+      </c>
+      <c r="U8" s="8">
+        <f t="shared" si="0"/>
+        <v>4.1608162267574578E-2</v>
+      </c>
+      <c r="V8" s="8">
+        <f t="shared" si="0"/>
+        <v>0.34938044141334368</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A9" s="9">
+        <f>'Proximal Validation (single)'!A9</f>
+        <v>0.7</v>
+      </c>
+      <c r="B9" s="9">
+        <f>'Proximal Validation (single)'!B9</f>
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="9">
+        <f>'Proximal Validation (single)'!C9</f>
+        <v>1.571</v>
+      </c>
+      <c r="D9" s="9">
+        <f>'Proximal Validation (single)'!D9</f>
+        <v>1.571</v>
+      </c>
+      <c r="E9" s="9">
+        <f>'Proximal Validation (single)'!E9</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="9">
+        <f>'Proximal Validation (single)'!F9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="9">
+        <f>'Proximal Validation (single)'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <f>'Proximal Validation (single)'!H9</f>
+        <v>8.7637116666883198E-4</v>
+      </c>
+      <c r="I9" s="9">
+        <f>'Proximal Validation (single)'!I9</f>
+        <v>-0.164488449692726</v>
+      </c>
+      <c r="J9" s="9">
+        <f>'Proximal Validation (single)'!J9</f>
+        <v>3.7763002328574701E-3</v>
+      </c>
+      <c r="K9" s="9">
+        <f>'Proximal Validation (single)'!K9</f>
+        <v>-0.58729076385498002</v>
+      </c>
+      <c r="L9" s="9">
+        <f>'Proximal Validation (single)'!L9</f>
+        <v>7.8071318566799199E-3</v>
+      </c>
+      <c r="M9" s="9">
+        <f>'Proximal Validation (single)'!M9</f>
+        <v>0.38755592703819303</v>
+      </c>
+      <c r="N9" s="9">
+        <v>0.81335304547649512</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0.19568796412024611</v>
+      </c>
+      <c r="P9" s="9">
+        <v>1.5342054081329517</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>1.7973528864566075</v>
+      </c>
+      <c r="R9" s="10">
+        <v>5.8710004116084829E-4</v>
+      </c>
+      <c r="S9" s="8">
+        <f t="shared" si="2"/>
+        <v>0.11335304547649516</v>
+      </c>
+      <c r="T9" s="8">
+        <f t="shared" si="0"/>
+        <v>4.3120358797539005E-3</v>
+      </c>
+      <c r="U9" s="8">
+        <f t="shared" si="0"/>
+        <v>3.6794591867048254E-2</v>
+      </c>
+      <c r="V9" s="8">
+        <f t="shared" si="0"/>
+        <v>0.22635288645660756</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A10" s="9">
+        <f>'Proximal Validation (single)'!A10</f>
+        <v>0.7</v>
+      </c>
+      <c r="B10" s="9">
+        <f>'Proximal Validation (single)'!B10</f>
+        <v>0.06</v>
+      </c>
+      <c r="C10" s="9">
+        <f>'Proximal Validation (single)'!C10</f>
+        <v>3.665</v>
+      </c>
+      <c r="D10" s="9">
+        <f>'Proximal Validation (single)'!D10</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E10" s="9">
+        <f>'Proximal Validation (single)'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <f>'Proximal Validation (single)'!F10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <f>'Proximal Validation (single)'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <f>'Proximal Validation (single)'!H10</f>
+        <v>-8.6323916912078901E-4</v>
+      </c>
+      <c r="I10" s="9">
+        <f>'Proximal Validation (single)'!I10</f>
+        <v>4.2902048677205998E-2</v>
+      </c>
+      <c r="J10" s="9">
+        <f>'Proximal Validation (single)'!J10</f>
+        <v>-8.0319754779338795E-2</v>
+      </c>
+      <c r="K10" s="9">
+        <f>'Proximal Validation (single)'!K10</f>
+        <v>0.61245459318161</v>
+      </c>
+      <c r="L10" s="9">
+        <f>'Proximal Validation (single)'!L10</f>
+        <v>-0.54026973247528098</v>
+      </c>
+      <c r="M10" s="9">
+        <f>'Proximal Validation (single)'!M10</f>
+        <v>-0.28817486763000499</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0.77039181014948266</v>
+      </c>
+      <c r="O10" s="9">
+        <v>9.8122259243736243E-2</v>
+      </c>
+      <c r="P10" s="9">
+        <v>3.6156391693223391</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0.7662535604327283</v>
+      </c>
+      <c r="R10" s="10">
+        <v>1.6319384535927404E-4</v>
+      </c>
+      <c r="S10" s="8">
+        <f t="shared" si="2"/>
+        <v>7.0391810149482703E-2</v>
+      </c>
+      <c r="T10" s="8">
+        <f t="shared" si="0"/>
+        <v>3.8122259243736245E-2</v>
+      </c>
+      <c r="U10" s="8">
+        <f t="shared" si="0"/>
+        <v>4.936083067766095E-2</v>
+      </c>
+      <c r="V10" s="8">
+        <f t="shared" si="0"/>
+        <v>1.8746439567271733E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A11" s="9">
+        <f>'Proximal Validation (single)'!A11</f>
+        <v>0.6</v>
+      </c>
+      <c r="B11" s="9">
+        <f>'Proximal Validation (single)'!B11</f>
+        <v>0.1</v>
+      </c>
+      <c r="C11" s="9">
+        <f>'Proximal Validation (single)'!C11</f>
+        <v>3.665</v>
+      </c>
+      <c r="D11" s="9">
+        <f>'Proximal Validation (single)'!D11</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E11" s="9">
+        <f>'Proximal Validation (single)'!E11</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="9">
+        <f>'Proximal Validation (single)'!F11</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <f>'Proximal Validation (single)'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <f>'Proximal Validation (single)'!H11</f>
+        <v>-8.0120982602238698E-4</v>
+      </c>
+      <c r="I11" s="9">
+        <f>'Proximal Validation (single)'!I11</f>
+        <v>4.2666438966989503E-2</v>
+      </c>
+      <c r="J11" s="9">
+        <f>'Proximal Validation (single)'!J11</f>
+        <v>-8.0293677747249603E-2</v>
+      </c>
+      <c r="K11" s="9">
+        <f>'Proximal Validation (single)'!K11</f>
+        <v>0.443310797214508</v>
+      </c>
+      <c r="L11" s="9">
+        <f>'Proximal Validation (single)'!L11</f>
+        <v>-0.42717015743255599</v>
+      </c>
+      <c r="M11" s="9">
+        <f>'Proximal Validation (single)'!M11</f>
+        <v>-0.22529536485672</v>
+      </c>
+      <c r="N11" s="9">
+        <v>0.56456072719100803</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0.16319523731678751</v>
+      </c>
+      <c r="P11" s="9">
+        <v>3.6059563354533699</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0.69432703009860464</v>
+      </c>
+      <c r="R11" s="10">
+        <v>1.5151190184287691E-4</v>
+      </c>
+      <c r="S11" s="8">
+        <f t="shared" si="2"/>
+        <v>3.5439272808991951E-2</v>
+      </c>
+      <c r="T11" s="8">
+        <f t="shared" si="0"/>
+        <v>6.31952373167875E-2</v>
+      </c>
+      <c r="U11" s="8">
+        <f t="shared" si="0"/>
+        <v>5.9043664546630126E-2</v>
+      </c>
+      <c r="V11" s="8">
+        <f t="shared" si="0"/>
+        <v>9.0672969901395395E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A12" s="9">
+        <f>'Proximal Validation (single)'!A12</f>
+        <v>0.8</v>
+      </c>
+      <c r="B12" s="9">
+        <f>'Proximal Validation (single)'!B12</f>
+        <v>0.18</v>
+      </c>
+      <c r="C12" s="9">
+        <f>'Proximal Validation (single)'!C12</f>
+        <v>3.665</v>
+      </c>
+      <c r="D12" s="9">
+        <f>'Proximal Validation (single)'!D12</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E12" s="9">
+        <f>'Proximal Validation (single)'!E12</f>
+        <v>1.4</v>
+      </c>
+      <c r="F12" s="9">
+        <f>'Proximal Validation (single)'!F12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <f>'Proximal Validation (single)'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <f>'Proximal Validation (single)'!H12</f>
+        <v>-5.5334065109491301E-5</v>
+      </c>
+      <c r="I12" s="9">
+        <f>'Proximal Validation (single)'!I12</f>
+        <v>7.7956624329090105E-2</v>
+      </c>
+      <c r="J12" s="9">
+        <f>'Proximal Validation (single)'!J12</f>
+        <v>-0.13737398386001601</v>
+      </c>
+      <c r="K12" s="9">
+        <f>'Proximal Validation (single)'!K12</f>
+        <v>0.41918036341667197</v>
+      </c>
+      <c r="L12" s="9">
+        <f>'Proximal Validation (single)'!L12</f>
+        <v>-0.55125319957733199</v>
+      </c>
+      <c r="M12" s="9">
+        <f>'Proximal Validation (single)'!M12</f>
+        <v>-0.30630308389663702</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0.68268348855866978</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="P12" s="9">
+        <v>3.6387187645288681</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0.75055341535926012</v>
+      </c>
+      <c r="R12" s="10">
+        <v>4.3757107107793996E-4</v>
+      </c>
+      <c r="S12" s="8">
+        <f t="shared" si="2"/>
+        <v>0.11731651144133026</v>
+      </c>
+      <c r="T12" s="8">
+        <f t="shared" si="0"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="U12" s="8">
+        <f t="shared" si="0"/>
+        <v>2.6281235471131925E-2</v>
+      </c>
+      <c r="V12" s="8">
+        <f t="shared" si="0"/>
+        <v>3.4446584640739908E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A13" s="9">
+        <f>'Proximal Validation (single)'!A13</f>
+        <v>0.4</v>
+      </c>
+      <c r="B13" s="9">
+        <f>'Proximal Validation (single)'!B13</f>
+        <v>0.2</v>
+      </c>
+      <c r="C13" s="9">
+        <f>'Proximal Validation (single)'!C13</f>
+        <v>3.665</v>
+      </c>
+      <c r="D13" s="9">
+        <f>'Proximal Validation (single)'!D13</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E13" s="9">
+        <f>'Proximal Validation (single)'!E13</f>
+        <v>1.4</v>
+      </c>
+      <c r="F13" s="9">
+        <f>'Proximal Validation (single)'!F13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
+        <f>'Proximal Validation (single)'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <f>'Proximal Validation (single)'!H13</f>
+        <v>-9.6024014055728899E-5</v>
+      </c>
+      <c r="I13" s="9">
+        <f>'Proximal Validation (single)'!I13</f>
+        <v>3.4424368292093298E-2</v>
+      </c>
+      <c r="J13" s="9">
+        <f>'Proximal Validation (single)'!J13</f>
+        <v>-6.16564750671387E-2</v>
+      </c>
+      <c r="K13" s="9">
+        <f>'Proximal Validation (single)'!K13</f>
+        <v>0.267098218202591</v>
+      </c>
+      <c r="L13" s="9">
+        <f>'Proximal Validation (single)'!L13</f>
+        <v>-0.21448078751564001</v>
+      </c>
+      <c r="M13" s="9">
+        <f>'Proximal Validation (single)'!M13</f>
+        <v>-0.115060687065125</v>
+      </c>
+      <c r="N13" s="9">
+        <v>0.27251414345506614</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="P13" s="9">
+        <v>3.6022784614867636</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0.931534869561914</v>
+      </c>
+      <c r="R13" s="10">
+        <v>7.375398737815166E-4</v>
+      </c>
+      <c r="S13" s="8">
+        <f t="shared" si="2"/>
+        <v>0.12748585654493388</v>
+      </c>
+      <c r="T13" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="8">
+        <f t="shared" si="0"/>
+        <v>6.2721538513236474E-2</v>
+      </c>
+      <c r="V13" s="8">
+        <f t="shared" si="0"/>
+        <v>0.14653486956191397</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A14" s="9">
+        <f>'Proximal Validation (single)'!A14</f>
+        <v>0.4</v>
+      </c>
+      <c r="B14" s="9">
+        <f>'Proximal Validation (single)'!B14</f>
+        <v>0.1</v>
+      </c>
+      <c r="C14" s="9">
+        <f>'Proximal Validation (single)'!C14</f>
+        <v>3.665</v>
+      </c>
+      <c r="D14" s="9">
+        <f>'Proximal Validation (single)'!D14</f>
+        <v>1.571</v>
+      </c>
+      <c r="E14" s="9">
+        <f>'Proximal Validation (single)'!E14</f>
+        <v>1.4</v>
+      </c>
+      <c r="F14" s="9">
+        <f>'Proximal Validation (single)'!F14</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <f>'Proximal Validation (single)'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <f>'Proximal Validation (single)'!H14</f>
+        <v>-3.7108035758137698E-4</v>
+      </c>
+      <c r="I14" s="9">
+        <f>'Proximal Validation (single)'!I14</f>
+        <v>3.7644270807504703E-2</v>
+      </c>
+      <c r="J14" s="9">
+        <f>'Proximal Validation (single)'!J14</f>
+        <v>-6.73996657133102E-2</v>
+      </c>
+      <c r="K14" s="9">
+        <f>'Proximal Validation (single)'!K14</f>
+        <v>1.67829748243093E-2</v>
+      </c>
+      <c r="L14" s="9">
+        <f>'Proximal Validation (single)'!L14</f>
+        <v>-0.33880779147148099</v>
+      </c>
+      <c r="M14" s="9">
+        <f>'Proximal Validation (single)'!M14</f>
+        <v>-0.185297966003418</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0.37803624346276793</v>
+      </c>
+      <c r="O14" s="9">
+        <v>0.16359079629866807</v>
+      </c>
+      <c r="P14" s="9">
+        <v>3.6155154530653713</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>1.7067986736798213</v>
+      </c>
+      <c r="R14" s="10">
+        <v>1.4150810867615636E-4</v>
+      </c>
+      <c r="S14" s="8">
+        <f t="shared" si="2"/>
+        <v>2.1963756537232093E-2</v>
+      </c>
+      <c r="T14" s="8">
+        <f t="shared" si="0"/>
+        <v>6.3590796298668067E-2</v>
+      </c>
+      <c r="U14" s="8">
+        <f t="shared" si="0"/>
+        <v>4.9484546934628781E-2</v>
+      </c>
+      <c r="V14" s="8">
+        <f t="shared" si="0"/>
+        <v>0.13579867367982135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A15" s="9">
+        <f>'Proximal Validation (single)'!A15</f>
+        <v>0.7</v>
+      </c>
+      <c r="B15" s="9">
+        <f>'Proximal Validation (single)'!B15</f>
+        <v>0.1</v>
+      </c>
+      <c r="C15" s="9">
+        <f>'Proximal Validation (single)'!C15</f>
+        <v>3.665</v>
+      </c>
+      <c r="D15" s="9">
+        <f>'Proximal Validation (single)'!D15</f>
+        <v>1.571</v>
+      </c>
+      <c r="E15" s="9">
+        <f>'Proximal Validation (single)'!E15</f>
+        <v>1.4</v>
+      </c>
+      <c r="F15" s="9">
+        <f>'Proximal Validation (single)'!F15</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
+        <f>'Proximal Validation (single)'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <f>'Proximal Validation (single)'!H15</f>
+        <v>-1.02429185062647E-3</v>
+      </c>
+      <c r="I15" s="9">
+        <f>'Proximal Validation (single)'!I15</f>
+        <v>7.0613205432891804E-2</v>
+      </c>
+      <c r="J15" s="9">
+        <f>'Proximal Validation (single)'!J15</f>
+        <v>-0.12678831815719599</v>
+      </c>
+      <c r="K15" s="9">
+        <f>'Proximal Validation (single)'!K15</f>
+        <v>-2.9671346768736801E-2</v>
+      </c>
+      <c r="L15" s="9">
+        <f>'Proximal Validation (single)'!L15</f>
+        <v>-0.63574087619781505</v>
+      </c>
+      <c r="M15" s="9">
+        <f>'Proximal Validation (single)'!M15</f>
+        <v>-0.34651768207549999</v>
+      </c>
+      <c r="N15" s="9">
+        <v>0.71745780640050827</v>
+      </c>
+      <c r="O15" s="9">
+        <v>0.13770541885089554</v>
+      </c>
+      <c r="P15" s="9">
+        <v>3.6275008130108692</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>1.552743408787387</v>
+      </c>
+      <c r="R15" s="10">
+        <v>1.5097595739252295E-4</v>
+      </c>
+      <c r="S15" s="8">
+        <f t="shared" si="2"/>
+        <v>1.7457806400508313E-2</v>
+      </c>
+      <c r="T15" s="8">
+        <f t="shared" si="0"/>
+        <v>3.7705418850895539E-2</v>
+      </c>
+      <c r="U15" s="8">
+        <f t="shared" si="0"/>
+        <v>3.7499186989130795E-2</v>
+      </c>
+      <c r="V15" s="8">
+        <f t="shared" si="0"/>
+        <v>1.8256591212612916E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A16" s="9">
+        <f>'Proximal Validation (single)'!A16</f>
+        <v>0.4</v>
+      </c>
+      <c r="B16" s="9">
+        <f>'Proximal Validation (single)'!B16</f>
+        <v>0.16</v>
+      </c>
+      <c r="C16" s="9">
+        <f>'Proximal Validation (single)'!C16</f>
+        <v>3.665</v>
+      </c>
+      <c r="D16" s="9">
+        <f>'Proximal Validation (single)'!D16</f>
+        <v>1.571</v>
+      </c>
+      <c r="E16" s="9">
+        <f>'Proximal Validation (single)'!E16</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <f>'Proximal Validation (single)'!F16</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <f>'Proximal Validation (single)'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <f>'Proximal Validation (single)'!H16</f>
+        <v>-6.0879066586494402E-4</v>
+      </c>
+      <c r="I16" s="9">
+        <f>'Proximal Validation (single)'!I16</f>
+        <v>4.7145899385213901E-2</v>
+      </c>
+      <c r="J16" s="9">
+        <f>'Proximal Validation (single)'!J16</f>
+        <v>-8.5028916597366305E-2</v>
+      </c>
+      <c r="K16" s="9">
+        <f>'Proximal Validation (single)'!K16</f>
+        <v>-7.4065491557121305E-2</v>
+      </c>
+      <c r="L16" s="9">
+        <f>'Proximal Validation (single)'!L16</f>
+        <v>-0.31546109914779702</v>
+      </c>
+      <c r="M16" s="9">
+        <f>'Proximal Validation (single)'!M16</f>
+        <v>-0.17043319344520599</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0.3901983724056291</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="P16" s="9">
+        <v>3.6089678133182845</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>1.6469615184258746</v>
+      </c>
+      <c r="R16" s="10">
+        <v>2.3391561709442866E-4</v>
+      </c>
+      <c r="S16" s="8">
+        <f t="shared" si="2"/>
+        <v>9.8016275943709208E-3</v>
+      </c>
+      <c r="T16" s="8">
+        <f t="shared" si="0"/>
+        <v>4.0000000000000008E-2</v>
+      </c>
+      <c r="U16" s="8">
+        <f t="shared" si="0"/>
+        <v>5.6032186681715501E-2</v>
+      </c>
+      <c r="V16" s="8">
+        <f t="shared" si="0"/>
+        <v>7.5961518425874619E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A17" s="9">
+        <f>'Proximal Validation (single)'!A17</f>
+        <v>0.3</v>
+      </c>
+      <c r="B17" s="9">
+        <f>'Proximal Validation (single)'!B17</f>
+        <v>0.18</v>
+      </c>
+      <c r="C17" s="9">
+        <f>'Proximal Validation (single)'!C17</f>
+        <v>3.665</v>
+      </c>
+      <c r="D17" s="9">
+        <f>'Proximal Validation (single)'!D17</f>
+        <v>1.571</v>
+      </c>
+      <c r="E17" s="9">
+        <f>'Proximal Validation (single)'!E17</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="9">
+        <f>'Proximal Validation (single)'!F17</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <f>'Proximal Validation (single)'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <f>'Proximal Validation (single)'!H17</f>
+        <v>3.8368394598364803E-5</v>
+      </c>
+      <c r="I17" s="9">
+        <f>'Proximal Validation (single)'!I17</f>
+        <v>3.2897148281335803E-2</v>
+      </c>
+      <c r="J17" s="9">
+        <f>'Proximal Validation (single)'!J17</f>
+        <v>-5.8571800589561497E-2</v>
+      </c>
+      <c r="K17" s="9">
+        <f>'Proximal Validation (single)'!K17</f>
+        <v>-6.3505612313747406E-2</v>
+      </c>
+      <c r="L17" s="9">
+        <f>'Proximal Validation (single)'!L17</f>
+        <v>-0.19738522171974199</v>
+      </c>
+      <c r="M17" s="9">
+        <f>'Proximal Validation (single)'!M17</f>
+        <v>-0.108248926699162</v>
+      </c>
+      <c r="N17" s="9">
+        <v>0.27706743788870136</v>
+      </c>
+      <c r="O17" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="P17" s="9">
+        <v>3.5977044030213592</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>2.0078134945690356</v>
+      </c>
+      <c r="R17" s="10">
+        <v>5.0781992633800897E-4</v>
+      </c>
+      <c r="S17" s="8">
+        <f t="shared" si="2"/>
+        <v>2.2932562111298627E-2</v>
+      </c>
       <c r="T17" s="8">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="U17" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>6.7295596978640848E-2</v>
       </c>
       <c r="V17" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>0.43681349456903562</v>
       </c>
     </row>
   </sheetData>
@@ -5367,9 +6527,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048D6981-73D2-4F8C-88D7-D5FA77AC2EB0}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="26" t="s">
         <v>23</v>
       </c>
@@ -5387,7 +6547,7 @@
       <c r="L1" s="27"/>
       <c r="M1" s="28"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -5425,7 +6585,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>0.19288232922553999</v>
       </c>
@@ -5469,7 +6629,7 @@
         <v>0.19288232922553999</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>0.27653545141220098</v>
       </c>
@@ -5513,7 +6673,7 @@
         <v>0.27653545141220098</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>0.52633810043335005</v>
       </c>
@@ -5557,7 +6717,7 @@
         <v>0.52633810043335005</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0.423814177513123</v>
       </c>
@@ -5601,7 +6761,7 @@
         <v>0.423814177513123</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>0.82944488525390603</v>
       </c>
@@ -5645,7 +6805,7 @@
         <v>0.82944488525390603</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>0.489793181419373</v>
       </c>
@@ -5689,7 +6849,7 @@
         <v>0.489793181419373</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>0.38755592703819303</v>
       </c>
@@ -5733,7 +6893,7 @@
         <v>0.38755592703819303</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>-0.28817486763000499</v>
       </c>
@@ -5777,7 +6937,7 @@
         <v>-0.28817486763000499</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>-0.22529536485672</v>
       </c>
@@ -5821,7 +6981,7 @@
         <v>-0.22529536485672</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>-0.30630308389663702</v>
       </c>
@@ -5865,7 +7025,7 @@
         <v>-0.30630308389663702</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>-0.115060687065125</v>
       </c>
@@ -5909,7 +7069,7 @@
         <v>-0.115060687065125</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>-0.185297966003418</v>
       </c>
@@ -5953,7 +7113,7 @@
         <v>-0.185297966003418</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>-0.34651768207549999</v>
       </c>
@@ -5997,7 +7157,7 @@
         <v>-0.34651768207549999</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>-0.17043319344520599</v>
       </c>
@@ -6041,7 +7201,7 @@
         <v>-0.17043319344520599</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>-0.108248926699162</v>
       </c>
@@ -6085,7 +7245,7 @@
         <v>-0.108248926699162</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H18">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6111,7 +7271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H19">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6137,7 +7297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H20">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6163,7 +7323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6189,7 +7349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H22">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6215,7 +7375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6241,7 +7401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6267,7 +7427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6293,7 +7453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H26">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6319,7 +7479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H27">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6345,7 +7505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H28">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6376,6 +7536,451 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="H1:M1"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17D690C-8097-4FB5-A9E3-5EAFC6B1E284}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1">
+        <v>2.6342464843764901E-4</v>
+      </c>
+      <c r="B1">
+        <v>-3.2978262752294499E-2</v>
+      </c>
+      <c r="C1">
+        <v>5.6162860710173802E-4</v>
+      </c>
+      <c r="D1">
+        <v>0.185834720730782</v>
+      </c>
+      <c r="E1">
+        <v>1.13257020711899E-3</v>
+      </c>
+      <c r="F1">
+        <v>0.19288232922553999</v>
+      </c>
+      <c r="G1">
+        <v>1.4</v>
+      </c>
+      <c r="H1">
+        <v>0</v>
+      </c>
+      <c r="I1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>-4.3474312406033299E-4</v>
+      </c>
+      <c r="B2">
+        <v>-6.2425632029771798E-2</v>
+      </c>
+      <c r="C2">
+        <v>2.5845002382993698E-3</v>
+      </c>
+      <c r="D2">
+        <v>0.25303724408149703</v>
+      </c>
+      <c r="E2">
+        <v>1.07369087636471E-2</v>
+      </c>
+      <c r="F2">
+        <v>0.27653545141220098</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>5.3234044462442398E-3</v>
+      </c>
+      <c r="B3">
+        <v>-0.12275674194097499</v>
+      </c>
+      <c r="C3">
+        <v>-8.3989212289452605E-3</v>
+      </c>
+      <c r="D3">
+        <v>0.26806160807609603</v>
+      </c>
+      <c r="E3">
+        <v>-2.4467468261718799E-2</v>
+      </c>
+      <c r="F3">
+        <v>0.52633810043335005</v>
+      </c>
+      <c r="G3">
+        <v>1.4</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>6.7002582363784302E-4</v>
+      </c>
+      <c r="B4">
+        <v>-6.6750191152095795E-2</v>
+      </c>
+      <c r="C4">
+        <v>1.6002767952158999E-3</v>
+      </c>
+      <c r="D4">
+        <v>-3.97013984620571E-2</v>
+      </c>
+      <c r="E4">
+        <v>7.3561742901802098E-3</v>
+      </c>
+      <c r="F4">
+        <v>0.423814177513123</v>
+      </c>
+      <c r="G4">
+        <v>1.4</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>7.4092089198529699E-4</v>
+      </c>
+      <c r="B5">
+        <v>-0.14775538444519001</v>
+      </c>
+      <c r="C5">
+        <v>3.4220633096993E-3</v>
+      </c>
+      <c r="D5">
+        <v>-0.161362335085869</v>
+      </c>
+      <c r="E5">
+        <v>2.0262047648429898E-2</v>
+      </c>
+      <c r="F5">
+        <v>0.82944488525390603</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>6.6551081836223602E-3</v>
+      </c>
+      <c r="B6">
+        <v>-0.148307904601097</v>
+      </c>
+      <c r="C6">
+        <v>-1.0527462000027299E-3</v>
+      </c>
+      <c r="D6">
+        <v>-0.444706320762634</v>
+      </c>
+      <c r="E6">
+        <v>-2.19946205615997E-2</v>
+      </c>
+      <c r="F6">
+        <v>0.489793181419373</v>
+      </c>
+      <c r="G6">
+        <v>1.4</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>8.7637116666883198E-4</v>
+      </c>
+      <c r="B7">
+        <v>-0.164488449692726</v>
+      </c>
+      <c r="C7">
+        <v>3.7763002328574701E-3</v>
+      </c>
+      <c r="D7">
+        <v>-0.58729076385498002</v>
+      </c>
+      <c r="E7">
+        <v>7.8071318566799199E-3</v>
+      </c>
+      <c r="F7">
+        <v>0.38755592703819303</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>-8.6323916912078901E-4</v>
+      </c>
+      <c r="B8">
+        <v>4.2902048677205998E-2</v>
+      </c>
+      <c r="C8">
+        <v>-8.0319754779338795E-2</v>
+      </c>
+      <c r="D8">
+        <v>0.61245459318161</v>
+      </c>
+      <c r="E8">
+        <v>-0.54026973247528098</v>
+      </c>
+      <c r="F8">
+        <v>-0.28817486763000499</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>-8.0120982602238698E-4</v>
+      </c>
+      <c r="B9">
+        <v>4.2666438966989503E-2</v>
+      </c>
+      <c r="C9">
+        <v>-8.0293677747249603E-2</v>
+      </c>
+      <c r="D9">
+        <v>0.443310797214508</v>
+      </c>
+      <c r="E9">
+        <v>-0.42717015743255599</v>
+      </c>
+      <c r="F9">
+        <v>-0.22529536485672</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>-5.5334065109491301E-5</v>
+      </c>
+      <c r="B10">
+        <v>7.7956624329090105E-2</v>
+      </c>
+      <c r="C10">
+        <v>-0.13737398386001601</v>
+      </c>
+      <c r="D10">
+        <v>0.41918036341667197</v>
+      </c>
+      <c r="E10">
+        <v>-0.55125319957733199</v>
+      </c>
+      <c r="F10">
+        <v>-0.30630308389663702</v>
+      </c>
+      <c r="G10">
+        <v>1.4</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>-9.6024014055728899E-5</v>
+      </c>
+      <c r="B11">
+        <v>3.4424368292093298E-2</v>
+      </c>
+      <c r="C11">
+        <v>-6.16564750671387E-2</v>
+      </c>
+      <c r="D11">
+        <v>0.267098218202591</v>
+      </c>
+      <c r="E11">
+        <v>-0.21448078751564001</v>
+      </c>
+      <c r="F11">
+        <v>-0.115060687065125</v>
+      </c>
+      <c r="G11">
+        <v>1.4</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>-3.7108035758137698E-4</v>
+      </c>
+      <c r="B12">
+        <v>3.7644270807504703E-2</v>
+      </c>
+      <c r="C12">
+        <v>-6.73996657133102E-2</v>
+      </c>
+      <c r="D12">
+        <v>1.67829748243093E-2</v>
+      </c>
+      <c r="E12">
+        <v>-0.33880779147148099</v>
+      </c>
+      <c r="F12">
+        <v>-0.185297966003418</v>
+      </c>
+      <c r="G12">
+        <v>1.4</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>-1.02429185062647E-3</v>
+      </c>
+      <c r="B13">
+        <v>7.0613205432891804E-2</v>
+      </c>
+      <c r="C13">
+        <v>-0.12678831815719599</v>
+      </c>
+      <c r="D13">
+        <v>-2.9671346768736801E-2</v>
+      </c>
+      <c r="E13">
+        <v>-0.63574087619781505</v>
+      </c>
+      <c r="F13">
+        <v>-0.34651768207549999</v>
+      </c>
+      <c r="G13">
+        <v>1.4</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>-6.0879066586494402E-4</v>
+      </c>
+      <c r="B14">
+        <v>4.7145899385213901E-2</v>
+      </c>
+      <c r="C14">
+        <v>-8.5028916597366305E-2</v>
+      </c>
+      <c r="D14">
+        <v>-7.4065491557121305E-2</v>
+      </c>
+      <c r="E14">
+        <v>-0.31546109914779702</v>
+      </c>
+      <c r="F14">
+        <v>-0.17043319344520599</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>3.8368394598364803E-5</v>
+      </c>
+      <c r="B15">
+        <v>3.2897148281335803E-2</v>
+      </c>
+      <c r="C15">
+        <v>-5.8571800589561497E-2</v>
+      </c>
+      <c r="D15">
+        <v>-6.3505612313747406E-2</v>
+      </c>
+      <c r="E15">
+        <v>-0.19738522171974199</v>
+      </c>
+      <c r="F15">
+        <v>-0.108248926699162</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6389,15 +7994,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E12580AD17ADB64691A1BA4C2E042DA4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6532fc6a52f3455fe895a4f720bca71c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xmlns:ns4="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9a2f75daf18a7097de825f86ff3fec6" ns3:_="" ns4:_="">
     <xsd:import namespace="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
@@ -6650,6 +8246,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
@@ -6668,14 +8273,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65923CC5-95C4-4597-AADE-A0DCE38786F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6692,4 +8289,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>